--- a/july 2026/GT_JULY_26/20-07-2026/Umair ok.xlsx
+++ b/july 2026/GT_JULY_26/20-07-2026/Umair ok.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC74E9C-27CB-4728-A11B-0CAFC8804B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8501A18A-4245-4989-B3B2-420F364F0D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3266,7 +3266,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -3294,7 +3294,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -4489,7 +4489,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -4517,7 +4517,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -5710,7 +5710,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -5738,7 +5738,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -6933,7 +6933,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -6961,7 +6961,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -8150,7 +8150,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -8178,7 +8178,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -9367,7 +9367,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -9395,7 +9395,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -10584,7 +10584,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -10612,7 +10612,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -11801,7 +11801,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -11829,7 +11829,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -13018,7 +13018,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -13046,7 +13046,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -14235,7 +14235,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -14263,7 +14263,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -18202,7 +18202,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -18230,7 +18230,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -19419,7 +19419,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -19447,7 +19447,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -20636,7 +20636,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -20664,7 +20664,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -21853,7 +21853,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -21881,7 +21881,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -23072,7 +23072,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -23100,7 +23100,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -24657,7 +24657,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -24685,7 +24685,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -26159,7 +26159,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -26187,7 +26187,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -27378,7 +27378,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -27406,7 +27406,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -28600,7 +28600,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -28628,7 +28628,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -29817,7 +29817,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -29845,7 +29845,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
@@ -31036,7 +31036,7 @@
       <c r="M4" s="238"/>
       <c r="N4" s="252">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="O4" s="252"/>
       <c r="P4" s="252"/>
@@ -31064,7 +31064,7 @@
       <c r="M5" s="238"/>
       <c r="N5" s="252">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O5" s="239"/>
       <c r="P5" s="239"/>
